--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487773_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487773_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8098</v>
+        <v>6.8959</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2777</v>
+        <v>4.3018</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5321</v>
+        <v>2.5941</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1154</v>
+        <v>2.7463</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9104</v>
+        <v>-0.3773</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2051</v>
+        <v>3.1236</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9769</v>
+        <v>3.2323</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3513</v>
+        <v>-0.3158</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6256</v>
+        <v>3.5482</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8615</v>
+        <v>-0.486</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5591</v>
+        <v>-0.0614</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4206</v>
+        <v>-0.4245</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8731</v>
+        <v>2.7055</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2487</v>
+        <v>-0.2081</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1218</v>
+        <v>2.9137</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2375</v>
+        <v>0.2765</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2643</v>
+        <v>0.11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5018</v>
+        <v>0.1664</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. TAIWO</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3626</v>
+        <v>6.6951</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5204</v>
+        <v>4.5153</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8422</v>
+        <v>2.1798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2326</v>
+        <v>4.1154</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6988</v>
+        <v>2.9104</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4662</v>
+        <v>1.2051</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4125</v>
+        <v>4.9769</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7071</v>
+        <v>2.3513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7054</v>
+        <v>2.6256</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1798</v>
+        <v>-0.8615</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0083</v>
+        <v>0.5591</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1716</v>
+        <v>-1.4206</v>
       </c>
       <c r="P3" t="n">
         <v>1.8731</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9137</v>
+        <v>3.1218</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3381</v>
+        <v>0.1228</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2297</v>
+        <v>-0.0266</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1084</v>
+        <v>0.1495</v>
       </c>
       <c r="V3" t="n">
-        <v>2.9188</v>
+        <v>0.5838</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9188</v>
+        <v>0.8137</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>S. TAIWO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7869</v>
+        <v>5.3041</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4864</v>
+        <v>3.5794</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3005</v>
+        <v>1.7247</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7463</v>
+        <v>0.2326</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3773</v>
+        <v>0.6988</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1236</v>
+        <v>-0.4662</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2323</v>
+        <v>1.4125</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3158</v>
+        <v>0.7071</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5482</v>
+        <v>0.7054</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.486</v>
+        <v>-1.1798</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0614</v>
+        <v>-0.0083</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4245</v>
+        <v>-1.1716</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7055</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
         <v>2.9137</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8325</v>
+        <v>0.2796</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7053</v>
+        <v>0.2886</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1272</v>
+        <v>-0.0091</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1675</v>
+        <v>2.9188</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>2.9188</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8476</v>
+        <v>4.4152</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2651</v>
+        <v>2.0089</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5825</v>
+        <v>2.4063</v>
       </c>
       <c r="G5" t="n">
         <v>2.2</v>
@@ -844,13 +844,13 @@
         <v>2.0812</v>
       </c>
       <c r="S5" t="n">
-        <v>1.939</v>
+        <v>1.5066</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0497</v>
+        <v>0.7935</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8893</v>
+        <v>0.7131</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1238</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2693</v>
+        <v>3.2861</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8519</v>
+        <v>1.81</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4174</v>
+        <v>1.4762</v>
       </c>
       <c r="G6" t="n">
         <v>3.8734</v>
@@ -922,13 +922,13 @@
         <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5447</v>
+        <v>-0.5279</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1924</v>
+        <v>0.1505</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7372</v>
+        <v>-0.6785</v>
       </c>
       <c r="V6" t="n">
         <v>1.3975</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0303</v>
+        <v>1.501</v>
       </c>
       <c r="E7" t="n">
-        <v>1.052</v>
+        <v>0.5815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9196</v>
       </c>
       <c r="G7" t="n">
         <v>0.7773</v>
@@ -1000,13 +1000,13 @@
         <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4829</v>
+        <v>0.9537</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0497</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4332</v>
+        <v>0.3745</v>
       </c>
       <c r="V7" t="n">
         <v>-0.23</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6857</v>
+        <v>1.4731</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4826</v>
+        <v>1.9765</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.5033</v>
       </c>
       <c r="G8" t="n">
         <v>0.8436</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4691</v>
+        <v>0.3184</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4443</v>
+        <v>0.0496</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0248</v>
+        <v>0.2688</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9376</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BARNES HERNANDEZ</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3394</v>
+        <v>0.4547</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8142</v>
+        <v>-0.8905</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1536</v>
+        <v>1.3452</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2716</v>
+        <v>0.9952</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1898</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4614</v>
+        <v>0.9291</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6183999999999999</v>
+        <v>2.5669</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0959</v>
+        <v>-0.3542</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7144</v>
+        <v>2.9211</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6532</v>
+        <v>-1.5717</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0939</v>
+        <v>0.4203</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.747</v>
+        <v>-1.9921</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.3299</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>2.4974</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4247</v>
+        <v>0.2919</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1957</v>
+        <v>-0.1276</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.4195</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>L. BARNES HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4884</v>
+        <v>0.1889</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5987</v>
+        <v>-0.6418</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1104</v>
+        <v>0.8306</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9952</v>
+        <v>-1.2716</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1898</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9291</v>
+        <v>-1.4614</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5669</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3542</v>
+        <v>0.0959</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9211</v>
+        <v>-0.7144</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5717</v>
+        <v>-0.6532</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4203</v>
+        <v>0.0939</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.9921</v>
+        <v>-0.747</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6511</v>
+        <v>0.2742</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8358</v>
+        <v>-0.0233</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1847</v>
+        <v>0.2975</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4107</v>
+        <v>-1.1144</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8334</v>
+        <v>-0.5957</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5774</v>
+        <v>-0.5187</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3194</v>
@@ -1312,13 +1312,13 @@
         <v>0.2081</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2995</v>
+        <v>-0.0031</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1957</v>
+        <v>0.0419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1357</v>
+        <v>-3.0243</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3012</v>
+        <v>0.3246</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4369</v>
+        <v>-3.3489</v>
       </c>
       <c r="G12" t="n">
         <v>-0.06759999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6061</v>
+        <v>-0.4947</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.199</v>
+        <v>-0.1757</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4071</v>
+        <v>-0.319</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5026</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>25.0968</v>
+        <v>26.0754</v>
       </c>
       <c r="E13" t="n">
-        <v>15.991</v>
+        <v>16.97</v>
       </c>
       <c r="F13" t="n">
-        <v>9.1058</v>
+        <v>9.105600000000001</v>
       </c>
       <c r="G13" t="n">
         <v>13.1252</v>
@@ -1468,19 +1468,19 @@
         <v>20.8119</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0192</v>
+        <v>2.998000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6814000000000002</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3379</v>
+        <v>1.3377</v>
       </c>
       <c r="V13" t="n">
-        <v>1.627400000000001</v>
+        <v>1.6274</v>
       </c>
       <c r="W13" t="n">
-        <v>6.403700000000001</v>
+        <v>6.403699999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-4.7763</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. ZIZIC</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.638</v>
+        <v>0.8484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5344</v>
+        <v>2.825</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1036</v>
+        <v>-1.9766</v>
       </c>
       <c r="G14" t="n">
-        <v>1.668</v>
+        <v>0.7347</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5161</v>
+        <v>-1.5587</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1519</v>
+        <v>2.2933</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2275</v>
+        <v>3.4822</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1491</v>
+        <v>-0.1623</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0784</v>
+        <v>3.6445</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5595</v>
+        <v>-2.7475</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6329</v>
+        <v>-1.3963</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0735</v>
+        <v>-1.3512</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7457</v>
+        <v>-0.9964</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6524</v>
+        <v>-0.6572</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.3392</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7005</v>
+        <v>-0.3467</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7005</v>
+        <v>-0.3467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>C. ZIZIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3547</v>
+        <v>0.754</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5035</v>
+        <v>0.8559</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1488</v>
+        <v>-0.1019</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7347</v>
+        <v>1.668</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.5587</v>
+        <v>1.5161</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2933</v>
+        <v>0.1519</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4822</v>
+        <v>2.2275</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1623</v>
+        <v>2.1491</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6445</v>
+        <v>0.0784</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7475</v>
+        <v>-0.5595</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3963</v>
+        <v>-0.6329</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3512</v>
+        <v>0.0735</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
         <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4901</v>
+        <v>-0.6297</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9786</v>
+        <v>-0.331</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5115</v>
+        <v>-0.2988</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3467</v>
+        <v>-0.7005</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3467</v>
+        <v>-0.7005</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0044</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3811</v>
+        <v>0.274</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4545</v>
+        <v>-0.2784</v>
       </c>
       <c r="G16" t="n">
         <v>0.1354</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2075</v>
+        <v>0.2765</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4534</v>
+        <v>0.3462</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2459</v>
+        <v>-0.0698</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6156</v>
+        <v>-2.2013</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2493</v>
+        <v>-0.5708</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3662</v>
+        <v>-1.6305</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9085</v>
@@ -1780,13 +1780,13 @@
         <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3335</v>
+        <v>0.7478</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7111</v>
+        <v>0.3896</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.3582</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3694</v>
+        <v>-2.34</v>
       </c>
       <c r="E18" t="n">
         <v>-3.4617</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0923</v>
+        <v>1.1217</v>
       </c>
       <c r="G18" t="n">
         <v>0.3942</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2662</v>
+        <v>-0.2368</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4567</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1905</v>
+        <v>0.2199</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6922</v>
+        <v>-2.8272</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3006</v>
+        <v>-1.1317</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3916</v>
+        <v>-1.6955</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.6111</v>
+        <v>-2.0391</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.678</v>
+        <v>0.1367</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0669</v>
+        <v>-2.1758</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3246</v>
+        <v>1.3086</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.8855</v>
+        <v>1.4923</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5609</v>
+        <v>-0.1837</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2865</v>
+        <v>-3.3477</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7925</v>
+        <v>-1.3556</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4939</v>
+        <v>-1.9921</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5976</v>
+        <v>-0.6089</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7078</v>
+        <v>-0.359</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1102</v>
+        <v>-0.2498</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1132</v>
+        <v>0.237</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2843</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7347</v>
+        <v>-2.9655</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3512</v>
+        <v>-0.494</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3834</v>
+        <v>-2.4715</v>
       </c>
       <c r="G20" t="n">
         <v>-1.868</v>
@@ -2014,13 +2014,13 @@
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3692</v>
+        <v>0.3999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8482</v>
+        <v>0.0091</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4789</v>
+        <v>0.3908</v>
       </c>
       <c r="V20" t="n">
         <v>0.5838</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8963</v>
+        <v>-4.3581</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8818</v>
+        <v>-3.0507</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0145</v>
+        <v>-1.3075</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0391</v>
+        <v>-4.6111</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1367</v>
+        <v>-4.678</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1758</v>
+        <v>0.0669</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3086</v>
+        <v>-2.3246</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4923</v>
+        <v>-2.8855</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1837</v>
+        <v>0.5609</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3477</v>
+        <v>-2.2865</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3556</v>
+        <v>-1.7925</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9921</v>
+        <v>-0.4939</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.678</v>
+        <v>-0.0683</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1091</v>
+        <v>-0.0423</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5689</v>
+        <v>-0.026</v>
       </c>
       <c r="V21" t="n">
-        <v>0.237</v>
+        <v>0.1132</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X21" t="n">
-        <v>0.237</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9125</v>
+        <v>-5.4697</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6208</v>
+        <v>-2.5852</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2916</v>
+        <v>-2.8845</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5474</v>
@@ -2170,13 +2170,13 @@
         <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>1.173</v>
+        <v>0.6157</v>
       </c>
       <c r="T22" t="n">
-        <v>1.295</v>
+        <v>0.3306</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.122</v>
+        <v>0.2851</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7956</v>
+        <v>-5.8186</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6593</v>
+        <v>-1.7665</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1363</v>
+        <v>-4.0521</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0835</v>
@@ -2248,13 +2248,13 @@
         <v>1.4568</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7816</v>
+        <v>-0.8046</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.46</v>
+        <v>-0.5672</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3216</v>
+        <v>-0.2374</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3467</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-25.097</v>
+        <v>-24.3824</v>
       </c>
       <c r="E24" t="n">
         <v>-9.105700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-15.991</v>
+        <v>-15.2768</v>
       </c>
       <c r="G24" t="n">
         <v>-13.1253</v>
@@ -2302,7 +2302,7 @@
         <v>8.267999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6105999999999999</v>
+        <v>-0.6106000000000004</v>
       </c>
       <c r="L24" t="n">
         <v>8.878499999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.4871</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.019200000000001</v>
+        <v>-1.3048</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3377</v>
+        <v>-1.3379</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6814</v>
+        <v>0.03299999999999997</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6274</v>
